--- a/frontend/public/analyzewise-ornek-veri.xlsx
+++ b/frontend/public/analyzewise-ornek-veri.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd.mm.yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,10 +57,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -72,6 +71,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +498,7 @@
           <t>505257</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="7" t="n">
         <v>43476</v>
       </c>
       <c r="C2" t="n">
@@ -530,7 +530,7 @@
           <t>504787</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="7" t="n">
         <v>43479</v>
       </c>
       <c r="C3" t="n">
@@ -562,7 +562,7 @@
           <t>504787</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="7" t="n">
         <v>43479</v>
       </c>
       <c r="C4" t="n">
@@ -594,7 +594,7 @@
           <t>501710</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="7" t="n">
         <v>43482</v>
       </c>
       <c r="C5" t="n">
@@ -626,7 +626,7 @@
           <t>501710</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="7" t="n">
         <v>43482</v>
       </c>
       <c r="C6" t="n">
@@ -658,7 +658,7 @@
           <t>501710</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="7" t="n">
         <v>43482</v>
       </c>
       <c r="C7" t="n">
@@ -690,7 +690,7 @@
           <t>504788</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="7" t="n">
         <v>43482</v>
       </c>
       <c r="C8" t="n">
@@ -722,7 +722,7 @@
           <t>504788</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="7" t="n">
         <v>43482</v>
       </c>
       <c r="C9" t="n">
@@ -754,7 +754,7 @@
           <t>504788</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="7" t="n">
         <v>43482</v>
       </c>
       <c r="C10" t="n">
@@ -786,7 +786,7 @@
           <t>504788</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="7" t="n">
         <v>43482</v>
       </c>
       <c r="C11" t="n">
@@ -818,7 +818,7 @@
           <t>501711</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="7" t="n">
         <v>43489</v>
       </c>
       <c r="C12" t="n">
@@ -850,7 +850,7 @@
           <t>501711</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="7" t="n">
         <v>43489</v>
       </c>
       <c r="C13" t="n">
@@ -882,7 +882,7 @@
           <t>501711</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="7" t="n">
         <v>43489</v>
       </c>
       <c r="C14" t="n">
@@ -914,7 +914,7 @@
           <t>505258</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="7" t="n">
         <v>43547</v>
       </c>
       <c r="C15" t="n">
@@ -946,7 +946,7 @@
           <t>505258</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="7" t="n">
         <v>43547</v>
       </c>
       <c r="C16" t="n">
@@ -983,13 +983,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Müşteriyi tanımlayan no ya da kod</t>
+          <t>Müşteri no, kodu ya da e-postası (harf içerebilir)</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Müşteri No, CustomerID</t>
+          <t>Müşteri No, Cari Kodu, CustomerID</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>TransactionNo</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -1049,85 +1049,85 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Fatura / sipariş no; aynı sepetteki satırlar aynı no'yu taşır</t>
+          <t>İşlem tarihi (Excel tarih hücresi, 2026-10-22, 22.10.2026, 10/22/2026)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fatura No, Sipariş No, InvoiceNo, OrderID</t>
+          <t>Tarih, Satış Tarihi, InvoiceDate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Zorunlu</t>
+          <t>Price ya da TotalPrice zorunlu</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>İşlem tarihi (Excel tarih hücresi, 2026-10-22 ya da 22.10.2026)</t>
+          <t>Birim fiyat</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Tarih, InvoiceDate, OrderDate</t>
+          <t>Birim Fiyat, Fiyat, UnitPrice</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>TotalPrice</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Zorunlu</t>
+          <t>Price ya da TotalPrice zorunlu</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Satılan adet; iadeler (0 ve altı) analize alınmaz</t>
+          <t>Satır tutarı (adet × fiyat); birim fiyat yoksa buradan hesaplanır</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Adet, Miktar, Qty</t>
+          <t>Tutar, Toplam, Amount</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>TransactionNo</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Zorunlu</t>
+          <t>İsteğe bağlı</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Birim fiyat; satır tutarı Adet × Fiyat olarak hesaplanır</t>
+          <t>Fatura / sipariş no; yoksa aynı müşterinin aynı günkü satırları tek alışveriş sayılır</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Birim Fiyat, Fiyat, UnitPrice</t>
+          <t>Fatura No, Sipariş No, InvoiceNo, OrderID</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ProductNo</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1137,19 +1137,19 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Ürün kodu; ürün önerisi ekranı için gerekli</t>
+          <t>Satılan adet; yoksa 1 sayılır. 0 ve negatif satırlar (iade) analize alınmaz</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Ürün Kodu, Stok Kodu, StockCode, SKU</t>
+          <t>Adet, Miktar, Qty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ProductName</t>
+          <t>ProductNo</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1159,56 +1159,78 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Ürün adı; önerilerde kod yerine ad gösterilir</t>
+          <t>Ürün kodu; ürün önerileri için (yoksa ürün adı kullanılır)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Ürün Adı, Description</t>
+          <t>Ürün Kodu, Stok Kodu, SKU</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>ProductName</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>İsteğe bağlı</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Ürün adı</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Ürün Adı, Stok Adı, Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>İsteğe bağlı</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Ülke; birliktelik kuralları için kullanılır</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Ülke</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Ülke ya da bölge</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Ülke, Bölge</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Kurallar</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Her satır bir faturadaki bir ürün. En az 180 gün, tercihen 1 yıllık veri. Ek kolonlar sorun değil, yok sayılır.</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Her satır bir satış. En az 180 gün, tercihen 1 yıllık veri. Kolon adları farklıysa yükleme sonrası eşleştirme ekranında seçilir; fazladan kolonlar yok sayılır.</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
